--- a/artfynd/A 38253-2025 artfynd.xlsx
+++ b/artfynd/A 38253-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128695433</v>
       </c>
       <c r="B2" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38253-2025 artfynd.xlsx
+++ b/artfynd/A 38253-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128695433</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38253-2025 artfynd.xlsx
+++ b/artfynd/A 38253-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128695433</v>
       </c>
       <c r="B2" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38253-2025 artfynd.xlsx
+++ b/artfynd/A 38253-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128695433</v>
       </c>
       <c r="B2" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38253-2025 artfynd.xlsx
+++ b/artfynd/A 38253-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128695433</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38253-2025 artfynd.xlsx
+++ b/artfynd/A 38253-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128695433</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38253-2025 artfynd.xlsx
+++ b/artfynd/A 38253-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128695433</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38253-2025 artfynd.xlsx
+++ b/artfynd/A 38253-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128695433</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38253-2025 artfynd.xlsx
+++ b/artfynd/A 38253-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128695433</v>
       </c>
       <c r="B2" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38253-2025 artfynd.xlsx
+++ b/artfynd/A 38253-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128695433</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38253-2025 artfynd.xlsx
+++ b/artfynd/A 38253-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128695433</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>98678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
